--- a/Tests/ClubCoreTests/Fixtures/members.xlsx
+++ b/Tests/ClubCoreTests/Fixtures/members.xlsx
@@ -449,17 +449,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Bojan</t>
+          <t>Ivan</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Šurbatović</t>
+          <t>Šimić</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>bojan@example.com</t>
+          <t>ivan@example.com</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
